--- a/tame_output/ON/bt/strategyON_20231114.xlsx
+++ b/tame_output/ON/bt/strategyON_20231114.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>88.2%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>102.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,16 +1217,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>126.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.8%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1780"/>
+  <dimension ref="A1:G1781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132571069090908</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42466,6 +42466,29 @@
       </c>
       <c r="G1780" t="n">
         <v>4.371474918864152</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" s="2" t="n">
+        <v>45243</v>
+      </c>
+      <c r="B1781" t="n">
+        <v>3.11753708665523</v>
+      </c>
+      <c r="C1781" t="n">
+        <v>3.067121317473999</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>1.555576174865313</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>3.688995363106377</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>2.185208400931525</v>
+      </c>
+      <c r="G1781" t="n">
+        <v>4.378246358032915</v>
       </c>
     </row>
   </sheetData>
